--- a/projectFor3Lab/Sorting_Performance_Report.xlsx
+++ b/projectFor3Lab/Sorting_Performance_Report.xlsx
@@ -144,19 +144,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>393.0</v>
+        <v>487.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>149.0</v>
+        <v>82.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>209.0</v>
+        <v>195.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>132.0</v>
+        <v>76.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>60.0</v>
+        <v>113.0</v>
       </c>
     </row>
     <row r="3">
@@ -164,19 +164,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>447.0</v>
+        <v>376.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>113.0</v>
+        <v>83.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>87.0</v>
+        <v>72.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>100.0</v>
+        <v>189.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>-26.0</v>
+        <v>-11.0</v>
       </c>
     </row>
     <row r="4">
@@ -184,19 +184,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>371.0</v>
+        <v>379.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>182.0</v>
+        <v>83.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>79.0</v>
+        <v>73.0</v>
       </c>
       <c r="E4" t="n" s="0">
         <v>75.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>-103.0</v>
+        <v>-10.0</v>
       </c>
     </row>
     <row r="5">
@@ -204,19 +204,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>375.0</v>
+        <v>389.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>201.0</v>
+        <v>185.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>75.0</v>
+        <v>73.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>179.0</v>
+        <v>80.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>-126.0</v>
+        <v>-112.0</v>
       </c>
     </row>
     <row r="6">
@@ -224,19 +224,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>640.0</v>
+        <v>488.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>91.0</v>
+        <v>83.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>336.0</v>
+        <v>184.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>107.0</v>
+        <v>76.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>245.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="7">
@@ -244,19 +244,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>445.2</v>
+        <v>423.8</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>147.2</v>
+        <v>103.2</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>157.2</v>
+        <v>119.4</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>118.6</v>
+        <v>99.2</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>10.0</v>
+        <v>16.200000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/projectFor3Lab/Sorting_Performance_Report.xlsx
+++ b/projectFor3Lab/Sorting_Performance_Report.xlsx
@@ -144,19 +144,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>487.0</v>
+        <v>504.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>82.0</v>
+        <v>113.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>195.0</v>
+        <v>86.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>76.0</v>
+        <v>75.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>113.0</v>
+        <v>-27.0</v>
       </c>
     </row>
     <row r="3">
@@ -164,19 +164,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>376.0</v>
+        <v>413.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>83.0</v>
+        <v>281.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>72.0</v>
+        <v>74.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>189.0</v>
+        <v>80.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>-11.0</v>
+        <v>-207.0</v>
       </c>
     </row>
     <row r="4">
@@ -184,19 +184,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>379.0</v>
+        <v>489.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>83.0</v>
+        <v>102.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>73.0</v>
+        <v>168.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>75.0</v>
+        <v>99.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>-10.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="5">
@@ -204,19 +204,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>389.0</v>
+        <v>432.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>185.0</v>
+        <v>168.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>73.0</v>
+        <v>183.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>80.0</v>
+        <v>207.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>-112.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="6">
@@ -224,19 +224,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>488.0</v>
+        <v>446.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>83.0</v>
+        <v>96.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>184.0</v>
+        <v>84.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>76.0</v>
+        <v>80.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>101.0</v>
+        <v>-12.0</v>
       </c>
     </row>
     <row r="7">
@@ -244,19 +244,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>423.8</v>
+        <v>456.8</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>103.2</v>
+        <v>152.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>119.4</v>
+        <v>119.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>99.2</v>
+        <v>108.2</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>16.200000000000003</v>
+        <v>-33.0</v>
       </c>
     </row>
   </sheetData>
